--- a/data/processed/harmonization/Isotopes__Radiocarbon_age/10.3334_CDIAC_SPRUCE.005/10.3334_CDIAC_SPRUCE.005_soil_Isotopes__Radiocarbon_age.xlsx
+++ b/data/processed/harmonization/Isotopes__Radiocarbon_age/10.3334_CDIAC_SPRUCE.005/10.3334_CDIAC_SPRUCE.005_soil_Isotopes__Radiocarbon_age.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -634,12 +634,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Hu:5:-20--10</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Hu:5:-30--20</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2009,12 +2009,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4154,12 +4154,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4539,12 +4539,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6354,12 +6354,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6519,12 +6519,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6629,12 +6629,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>19:20-24</t>
+          <t>Hu:19:20-24</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7454,12 +7454,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7839,12 +7839,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
